--- a/artfynd/A 8708-2023 artfynd.xlsx
+++ b/artfynd/A 8708-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 8708-2023 artfynd.xlsx
+++ b/artfynd/A 8708-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2259,6 +2259,107 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128166104</v>
+      </c>
+      <c r="B15" t="n">
+        <v>56628</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>208260</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Vipera berus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Finkarsberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>765610</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7081243</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8708-2023 artfynd.xlsx
+++ b/artfynd/A 8708-2023 artfynd.xlsx
@@ -2264,7 +2264,7 @@
         <v>128166104</v>
       </c>
       <c r="B15" t="n">
-        <v>56628</v>
+        <v>56640</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 8708-2023 artfynd.xlsx
+++ b/artfynd/A 8708-2023 artfynd.xlsx
@@ -2264,7 +2264,7 @@
         <v>128166104</v>
       </c>
       <c r="B15" t="n">
-        <v>56640</v>
+        <v>56644</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 8708-2023 artfynd.xlsx
+++ b/artfynd/A 8708-2023 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1584409</v>
+        <v>138076</v>
       </c>
       <c r="B2" t="n">
-        <v>89355</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>765682.5095629152</v>
+        <v>765619</v>
       </c>
       <c r="R2" t="n">
-        <v>7081047.881517663</v>
+        <v>7080831</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,21 +743,11 @@
           <t>2010-10-31</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2010-10-31</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -779,7 +764,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>708605</v>
+        <v>138077</v>
       </c>
       <c r="B3" t="n">
-        <v>90840</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2079</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>765688.2430415361</v>
+        <v>765613</v>
       </c>
       <c r="R3" t="n">
-        <v>7081090.60299291</v>
+        <v>7080837</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,21 +850,11 @@
           <t>2010-10-31</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2010-10-31</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -901,7 +871,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -919,37 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1556872</v>
+        <v>7123949</v>
       </c>
       <c r="B4" t="n">
-        <v>89409</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80305</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>392</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -959,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>765687.9512180826</v>
+        <v>765627</v>
       </c>
       <c r="R4" t="n">
-        <v>7080867.831173084</v>
+        <v>7080796</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,41 +954,41 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2010-10-31</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-03-13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2010-10-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-03-13</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>inga sporer</t>
         </is>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>lövrik grannaturskog</t>
+          <t>naturskog</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>asp</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>granstubbe</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1041,37 +1006,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1846785</v>
+        <v>364044</v>
       </c>
       <c r="B5" t="n">
-        <v>77505</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1081,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>765689.0024589566</v>
+        <v>765678</v>
       </c>
       <c r="R5" t="n">
-        <v>7081102.67115578</v>
+        <v>7080879</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1114,21 +1074,11 @@
           <t>2010-10-31</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2010-10-31</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1145,7 +1095,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1163,15 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>138076</v>
+        <v>708605</v>
       </c>
       <c r="B6" t="n">
-        <v>77540</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1179,21 +1124,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>2079</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1203,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>765619.3966985481</v>
+        <v>765688</v>
       </c>
       <c r="R6" t="n">
-        <v>7080830.907453414</v>
+        <v>7081091</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,21 +1181,11 @@
           <t>2010-10-31</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2010-10-31</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1267,7 +1202,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1285,50 +1220,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>364044</v>
+        <v>128346986</v>
       </c>
       <c r="B7" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>4660</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Finkarsberget, Vb</t>
+          <t>Finkarsberget, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>765677.6971405952</v>
+        <v>765753</v>
       </c>
       <c r="R7" t="n">
-        <v>7080878.523616658</v>
+        <v>7081018</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,22 +1285,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2010-10-31</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2010-10-31</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,62 +1302,62 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>lövrik grannaturskog</t>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Carl Jansson, KajsaLisa Olsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1846784</v>
+        <v>1584409</v>
       </c>
       <c r="B8" t="n">
-        <v>77505</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1447,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>765633.7172242785</v>
+        <v>765683</v>
       </c>
       <c r="R8" t="n">
-        <v>7080872.134844378</v>
+        <v>7081048</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1480,21 +1400,11 @@
           <t>2010-10-31</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2010-10-31</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1511,7 +1421,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1529,37 +1439,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>138077</v>
+        <v>1846784</v>
       </c>
       <c r="B9" t="n">
-        <v>77540</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1569,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>765613.0899215976</v>
+        <v>765634</v>
       </c>
       <c r="R9" t="n">
-        <v>7080837.04328574</v>
+        <v>7080872</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1602,19 +1507,9 @@
           <t>2010-10-31</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2010-10-31</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1651,19 +1546,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1848998</v>
+        <v>1846785</v>
       </c>
       <c r="B10" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1691,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>765626.8048850368</v>
+        <v>765689</v>
       </c>
       <c r="R10" t="n">
-        <v>7080795.964048545</v>
+        <v>7081103</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1721,22 +1611,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2011-03-13</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-10-31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2011-03-13</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-10-31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1750,7 +1630,12 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>asprik blandnaturskog</t>
+          <t>lövrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1761,44 +1646,39 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Nils Ericson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1984752</v>
+        <v>1848998</v>
       </c>
       <c r="B11" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1808,10 +1688,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>765681.2890677473</v>
+        <v>765627</v>
       </c>
       <c r="R11" t="n">
-        <v>7080767.670923118</v>
+        <v>7080796</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1838,22 +1718,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2011-11-13</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-03-13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2011-11-13</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-03-13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1865,9 +1735,9 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>asp</t>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>asprik blandnaturskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1878,7 +1748,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Linda Nordström, Viktor Säfve, Elin Götmark, Anders Hellström, Daniel Rutschman</t>
+          <t>Andreas Garpebring, Nils Ericson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1888,12 +1758,7 @@
         <v>1896050</v>
       </c>
       <c r="B12" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>765682.2478874753</v>
+        <v>765682</v>
       </c>
       <c r="R12" t="n">
-        <v>7080766.862783004</v>
+        <v>7080767</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1958,19 +1823,9 @@
           <t>2011-11-13</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2011-11-13</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2002,37 +1857,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>7123949</v>
+        <v>1984752</v>
       </c>
       <c r="B13" t="n">
-        <v>78479</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>392</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2042,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>765626.8048850368</v>
+        <v>765681</v>
       </c>
       <c r="R13" t="n">
-        <v>7080795.964048545</v>
+        <v>7080768</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2072,47 +1922,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2011-03-13</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-11-13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2011-03-13</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>inga sporer</t>
+          <t>2011-11-13</t>
         </is>
       </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>naturskog</t>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -2127,7 +1952,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Andreas Garpebring, Linda Nordström, Viktor Säfve, Elin Götmark, Anders Hellström, Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2137,12 +1962,7 @@
         <v>100022927</v>
       </c>
       <c r="B14" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2174,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>765698.390055933</v>
+        <v>765698</v>
       </c>
       <c r="R14" t="n">
-        <v>7081139.032456118</v>
+        <v>7081139</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2207,19 +2027,9 @@
           <t>2022-04-17</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-04-17</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2264,7 +2074,7 @@
         <v>128166104</v>
       </c>
       <c r="B15" t="n">
-        <v>56644</v>
+        <v>56905</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 8708-2023 artfynd.xlsx
+++ b/artfynd/A 8708-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/138076</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/138077</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7123949</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1110,6 +1130,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/364044</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/708605</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1329,6 +1359,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346986</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1436,6 +1471,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1584409</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1543,6 +1583,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1846784</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1650,6 +1695,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1846785</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1752,6 +1802,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1848998</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1854,6 +1909,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1896050</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,6 +2016,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1984752</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2068,6 +2133,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100022927</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2169,8 +2239,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128166104</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>